--- a/Immigration_Networks/MigrationData/Matrices/DifferenceMatrices_2020.xlsx
+++ b/Immigration_Networks/MigrationData/Matrices/DifferenceMatrices_2020.xlsx
@@ -9,10 +9,10 @@
     <sheet name="RawMatrix" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="DiffMat" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="DiffMat_Pos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DiffMat_PopScaled" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="DiffMat_PopScaled_Per1000" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DiffMat_PopScaled_Pos" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DiffMat_PopScaled_Per1000_Pos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DiffMat_PopScaled_dest" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="DiffMat_PopScaled_org" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DiffMat_PopScaled_Per1000_dest" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="DiffMat_PopScaled_Per1000_org" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="DM_10000_binary" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
 </workbook>
@@ -4230,19 +4230,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0317811016799761</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.000058342776203966</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0.000536399745740311</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.00701810122379124</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0000593324151293155</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0.000325168111118902</v>
@@ -4269,19 +4269,19 @@
         <v>0.000672342214539047</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0874697057344805</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.0051671950264004</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0.000647318078428321</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0290814196843163</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0058726738064576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4304,7 +4304,7 @@
         <v>0.00637635628052044</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0000428994692612761</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0.0000556182474729949</v>
@@ -4313,25 +4313,25 @@
         <v>0.0000274705483805371</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0000139542202133135</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.000000748963333923862</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0000109040166863764</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0000686637009914773</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.00000860435283643246</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0.0000978036589229499</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.00051594537596575</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0.000473130810296564</v>
@@ -4340,10 +4340,10 @@
         <v>0.000225300310359146</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.000162649371137077</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.000135532709662491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -4354,7 +4354,7 @@
         <v>0.000272320015796632</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.00174987108907789</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4363,10 +4363,10 @@
         <v>0.000777629651996917</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.000032007229090813</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0000793008144954068</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0.0000321791288950899</v>
@@ -4375,10 +4375,10 @@
         <v>0.0000329988537600228</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.00000705730677454936</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.00000645260718457481</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0.00000807704939731581</v>
@@ -4387,7 +4387,7 @@
         <v>0.0000276423167664775</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0000511732563429931</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0.000404656844738082</v>
@@ -4396,16 +4396,16 @@
         <v>0.00421378757463332</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0000793403974189623</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.00149578560323978</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.00454122801714583</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.00852530283859088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4413,61 +4413,61 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.000449260811040718</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.000270389231010488</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.000139537299338999</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.00148456755962018</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.00145585629799662</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.000509105600976021</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.000778978122956807</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.00826474780634045</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.00104716596595386</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.000810430943903176</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.000592448375006776</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0015646336342039</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.000149023110633784</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00075541132763681</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.000793889236559157</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.00157301157083482</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.00191839895443802</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.000749227913689507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4478,7 +4478,7 @@
         <v>0.0029959168525915</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0104528499151892</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0.00000292728989612842</v>
@@ -4490,13 +4490,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.00333310310091466</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0.000414355943673812</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.00173298125437135</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0.0000372112539021694</v>
@@ -4508,7 +4508,7 @@
         <v>0.0000317024188844646</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0000298139914843826</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0.0000196239626094074</v>
@@ -4517,19 +4517,19 @@
         <v>0.000504778125910391</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.000527441984886726</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.00675297179224438</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.000219632682035528</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.00118489347185878</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0179056152179249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4561,7 +4561,7 @@
         <v>0.0105032102926332</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0000315974871496869</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0.0000221808371969759</v>
@@ -4588,10 +4588,10 @@
         <v>0.00240721334887436</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.000190573245473885</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0303395280760896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4599,61 +4599,61 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.000036075735684963</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0000236960828428597</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.000000764872521246459</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0.0000674380726151485</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.000107688838521671</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.000468141445870518</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0000284394266429212</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.00253309195205587</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.000111998824703691</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.000386587776779028</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.00000224923452925883</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.051259752732033</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.00101766792969354</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0000138800522338612</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.000118343360370333</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.00024680769097526</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.00010766524744295</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.000954883151392217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4661,13 +4661,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.00010318057084728</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.000040791114036637</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.00000273371104815864</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0.000359634637730725</v>
@@ -4676,7 +4676,7 @@
         <v>0.00156974808865218</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.00363993701204446</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0.0000991196624608015</v>
@@ -4685,37 +4685,37 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0000673652010297894</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0000156130048841051</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.00000191829923186251</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0.00000881079456978631</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0000442293926504335</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0.00050825455928443</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0000353310420498285</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.000046585187475354</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.00120019582562195</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.000288450743149295</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0124491400671123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4723,7 +4723,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.00000317343062836571</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0.00000736271145474569</v>
@@ -4735,7 +4735,7 @@
         <v>0.00135581311186632</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.00001197689862753</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0.000003890973961543</v>
@@ -4753,28 +4753,28 @@
         <v>0.000671013534631633</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.000283403470728319</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0.000116843855804429</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.000814998262524541</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0.000854970847788536</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.00000154222802598458</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.00000103118253526174</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.0042451956072098</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0000218784994803856</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0.0000250035694265778</v>
@@ -4785,7 +4785,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0000109968186357951</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0.00000110017527484706</v>
@@ -4797,10 +4797,10 @@
         <v>0.000478249866505243</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0000166231093020029</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.00000760418769134037</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0.000386149546741079</v>
@@ -4809,34 +4809,34 @@
         <v>0.0000154450593591816</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.00186810118189037</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.000435352962515322</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0.00021287065824151</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0011122258192778</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0.000371746608797184</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.00000869255796464036</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.00000555018835155585</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.00367836933124744</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0000428933739812824</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0.00000348150966699184</v>
@@ -4847,22 +4847,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.00000282082722521396</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0.00000913991766796016</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.000000377714825306893</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0.000211207728787279</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0000162101127976053</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.00000387122282468237</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0.000760579534193205</v>
@@ -4889,16 +4889,16 @@
         <v>0.000322381254885837</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.0000049070891735873</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.00000245664074577062</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0.00231445578361848</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0000192876245419189</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0.00000604868346184441</v>
@@ -4909,13 +4909,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.000335524175811583</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0.000749219362170846</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0000168271954674221</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0.00200988084852935</v>
@@ -4924,28 +4924,28 @@
         <v>0.00019844482036304</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.000288603611807443</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0.0000576046134541732</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0000647438650628426</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.00241632560360423</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.00158123443560572</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.00375199137128813</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.00051595926306888</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0.000934928815391422</v>
@@ -4960,10 +4960,10 @@
         <v>0.0303739470654572</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.000815837730623854</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.00234797935288934</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4971,7 +4971,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.00000418716541242698</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0.00000482384543586786</v>
@@ -4983,10 +4983,10 @@
         <v>0.000272725564828722</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.00000671119319646078</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.00000922378091391157</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0.0674516255326689</v>
@@ -5001,7 +5001,7 @@
         <v>0.000424489372642386</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.000521676427949135</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0.0000265099435207127</v>
@@ -5022,7 +5022,7 @@
         <v>0.000759006005664891</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0000109392497401928</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0.0000619638387195922</v>
@@ -5033,61 +5033,61 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0000639314045339509</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0000357133819988814</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.00000824362606232295</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0.0000169187205195242</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.000112438298322243</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.000939739340691646</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0.00087221330233543</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.000124985295847547</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.00059169101571165</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.000092410552893375</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.000140439696395829</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0000312876279001039</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.00227849301251073</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.0000203293694334331</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.000136813659310756</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0.000250442102954638</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.000263117743750954</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.00417517409306673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5101,7 +5101,7 @@
         <v>0.000311434231649013</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.000141902738432483</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0.000141769931818346</v>
@@ -5128,7 +5128,7 @@
         <v>0.00000353370911132567</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.00000898918213589994</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5146,7 +5146,7 @@
         <v>0.000134331250416481</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.000559341111715649</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0.00000703335286260978</v>
@@ -5160,7 +5160,7 @@
         <v>0.00375460918761057</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.00132021032981647</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.0000123512747875354</v>
@@ -5172,7 +5172,7 @@
         <v>0.0114946219595197</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.000167924165589028</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0.000775080005855807</v>
@@ -5190,16 +5190,16 @@
         <v>0.00000817801251478226</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.00000745349787109564</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.00000996293486323759</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0.00104547939668585</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.00014496943444255</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -5208,10 +5208,10 @@
         <v>0.00119206296024499</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.000367904241262274</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0315646326444633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5219,61 +5219,61 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.0047218884733066</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.00631119777859379</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.00233762511803588</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0136999799869692</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.00375305410915002</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0157375873437243</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0162274182466387</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0226414311494589</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.225380064038643</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0701461774783845</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0773469356229884</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0779775252297607</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.037924515371148</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0192123931605113</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.0062339660861253</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.0119670552951011</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.014258736286355</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0174092715064105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5335,7 +5335,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.000365347514448265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5367,25 +5367,25 @@
         <v>0.0201756359716914</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.000114039661743286</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.00000570364385065095</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.000017365656204229</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0.000517843592465601</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.000265980170136737</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0.0275159701555148</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.000028040509563356</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0.0272223090639671</v>
@@ -5481,58 +5481,58 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-31.7811016799761</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.058342776203966</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.536399745740311</v>
+        <v>0.000449260811040718</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.01810122379124</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0593324151293155</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.325168111118902</v>
+        <v>0.000036075735684963</v>
       </c>
       <c r="I2" t="n">
-        <v>0.266840472028371</v>
+        <v>0.00010318057084728</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0230966403530706</v>
+        <v>0.00000317343062836571</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0287486695098467</v>
+        <v>0.0000109968186357951</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0129232790357053</v>
+        <v>0.00000282082722521396</v>
       </c>
       <c r="M2" t="n">
-        <v>0.118084812786089</v>
+        <v>0.000335524175811583</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0286811761214415</v>
+        <v>0.00000418716541242698</v>
       </c>
       <c r="O2" t="n">
-        <v>0.672342214539047</v>
+        <v>0.0000639314045339509</v>
       </c>
       <c r="P2" t="n">
-        <v>-87.4697057344805</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.1671950264004</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.64731807842832</v>
+        <v>0.0047218884733066</v>
       </c>
       <c r="S2" t="n">
-        <v>-29.0814196843163</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-5.8726738064576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -5540,61 +5540,61 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>8.27593243766192</v>
+        <v>0.0317811016799761</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0976251180358829</v>
+        <v>0.00174987108907789</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0840673593466248</v>
+        <v>0.000270389231010488</v>
       </c>
       <c r="F3" t="n">
-        <v>6.37635628052044</v>
+        <v>0.0104528499151892</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0428994692612761</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0556182474729949</v>
+        <v>0.0000236960828428597</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0274705483805371</v>
+        <v>0.000040791114036637</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0139542202133135</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.000748963333923862</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0109040166863764</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0686637009914773</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.00860435283643246</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.09780365892295</v>
+        <v>0.0000357133819988814</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.51594537596575</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.473130810296564</v>
+        <v>0.00132021032981647</v>
       </c>
       <c r="R3" t="n">
-        <v>0.225300310359146</v>
+        <v>0.00631119777859379</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.162649371137077</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.135532709662491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -5602,61 +5602,61 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.272320015796632</v>
+        <v>0.000058342776203966</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.74987108907789</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.777629651996917</v>
+        <v>0.000139537299338999</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.032007229090813</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0793008144954068</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0321791288950899</v>
+        <v>0.000000764872521246459</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0329988537600228</v>
+        <v>0.00000273371104815864</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.00705730677454936</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.00645260718457481</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00807704939731582</v>
+        <v>0.000000377714825306893</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0276423167664775</v>
+        <v>0.0000168271954674221</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0511732563429931</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.404656844738082</v>
+        <v>0.00000824362606232295</v>
       </c>
       <c r="P4" t="n">
-        <v>4.21378757463332</v>
+        <v>0.000141902738432483</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0793403974189622</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49578560323978</v>
+        <v>0.00233762511803588</v>
       </c>
       <c r="S4" t="n">
-        <v>-4.54122801714583</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-8.52530283859088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -5664,61 +5664,61 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.449260811040718</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.270389231010488</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.139537299338999</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.48456755962018</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.45585629799662</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.509105600976021</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.778978122956807</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.26474780634044</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.04716596595386</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.810430943903176</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.592448375006776</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5646336342039</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.149023110633784</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.75541132763681</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.793889236559157</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.57301157083482</v>
+        <v>0.0136999799869692</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.91839895443802</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.749227913689507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5726,61 +5726,61 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2.9959168525915</v>
+        <v>0.00701810122379124</v>
       </c>
       <c r="C6" t="n">
-        <v>-10.4528499151892</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00292728989612842</v>
+        <v>0.000032007229090813</v>
       </c>
       <c r="E6" t="n">
-        <v>0.756658858444723</v>
+        <v>0.00148456755962018</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.33310310091466</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.414355943673812</v>
+        <v>0.000107688838521671</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.73298125437135</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0372112539021694</v>
+        <v>0.00001197689862753</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0185512456556526</v>
+        <v>0.0000166231093020029</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0317024188844646</v>
+        <v>0.0000162101127976053</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0298139914843826</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0196239626094074</v>
+        <v>0.00000671119319646078</v>
       </c>
       <c r="O6" t="n">
-        <v>0.504778125910391</v>
+        <v>0.000112438298322243</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.527441984886726</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.75297179224438</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.219632682035528</v>
+        <v>0.00375305410915002</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.18489347185878</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-17.9056152179249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5788,61 +5788,61 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0662012889417402</v>
+        <v>0.0000593324151293155</v>
       </c>
       <c r="C7" t="n">
-        <v>0.183813899766754</v>
+        <v>0.0000428994692612761</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0189565627950897</v>
+        <v>0.0000793008144954068</v>
       </c>
       <c r="E7" t="n">
-        <v>1.93946950154608</v>
+        <v>0.00145585629799662</v>
       </c>
       <c r="F7" t="n">
-        <v>8.71190313745184</v>
+        <v>0.00333310310091466</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.70808464858901</v>
+        <v>0.000468141445870518</v>
       </c>
       <c r="I7" t="n">
-        <v>10.5032102926332</v>
+        <v>0.00363993701204446</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0315974871496869</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0221808371969759</v>
+        <v>0.00000760418769134037</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0197887710234237</v>
+        <v>0.00000387122282468237</v>
       </c>
       <c r="M7" t="n">
-        <v>0.113330396350104</v>
+        <v>0.000288603611807443</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0704953118353326</v>
+        <v>0.00000922378091391157</v>
       </c>
       <c r="O7" t="n">
-        <v>11.0270149002252</v>
+        <v>0.000939739340691646</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.257856291611627</v>
+        <v>0.000167924165589028</v>
       </c>
       <c r="R7" t="n">
-        <v>2.40721334887436</v>
+        <v>0.0157375873437243</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.190573245473885</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-30.3395280760896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5850,61 +5850,61 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.036075735684963</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0236960828428597</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.000764872521246459</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0674380726151485</v>
+        <v>0.000509105600976021</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.107688838521671</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.468141445870518</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0284394266429212</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.53309195205587</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.111998824703691</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.386587776779028</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.00224923452925883</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-51.259752732033</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.01766792969354</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0138800522338612</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.118343360370333</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.246807690975261</v>
+        <v>0.0162274182466387</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.10766524744295</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.954883151392217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5912,61 +5912,61 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.10318057084728</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.040791114036637</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.00273371104815864</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.359634637730725</v>
+        <v>0.000778978122956807</v>
       </c>
       <c r="F9" t="n">
-        <v>1.56974808865218</v>
+        <v>0.00173298125437135</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.63993701204446</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0991196624608015</v>
+        <v>0.0000284394266429212</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0673652010297894</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0156130048841051</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.00191829923186251</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00881079456978631</v>
+        <v>0.0000647438650628426</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0442293926504335</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.50825455928443</v>
+        <v>0.000124985295847547</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0353310420498286</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.046585187475354</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.20019582562195</v>
+        <v>0.0226414311494589</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.288450743149295</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-12.4491400671123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5974,61 +5974,61 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.00317343062836571</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00736271145474569</v>
+        <v>0.0000139542202133135</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000207743153918791</v>
+        <v>0.00000705730677454936</v>
       </c>
       <c r="E10" t="n">
-        <v>1.35581311186632</v>
+        <v>0.00826474780634045</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.01197689862753</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003890973961543</v>
+        <v>0.0000315974871496869</v>
       </c>
       <c r="H10" t="n">
-        <v>3.13706779407503</v>
+        <v>0.00253309195205587</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0239369923647834</v>
+        <v>0.0000673652010297894</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.671013534631632</v>
+        <v>0.00186810118189037</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.283403470728319</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.116843855804429</v>
+        <v>0.00241632560360423</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.814998262524541</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.854970847788536</v>
+        <v>0.00059169101571165</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.00154222802598458</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.00103118253526174</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>4.2451956072098</v>
+        <v>0.225380064038643</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0218784994803856</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0250035694265778</v>
+        <v>0.000114039661743286</v>
       </c>
     </row>
     <row r="11">
@@ -6036,61 +6036,61 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0109968186357951</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00110017527484706</v>
+        <v>0.000000748963333923862</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000528800755429651</v>
+        <v>0.00000645260718457481</v>
       </c>
       <c r="E11" t="n">
-        <v>0.478249866505243</v>
+        <v>0.00104716596595386</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0166231093020029</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.00760418769134037</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.386149546741079</v>
+        <v>0.000111998824703691</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0154450593591816</v>
+        <v>0.0000156130048841051</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.86810118189037</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.435352962515322</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.21287065824151</v>
+        <v>0.00158123443560572</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1122258192778</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.371746608797184</v>
+        <v>0.000092410552893375</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.00869255796464036</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.00555018835155585</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.67836933124744</v>
+        <v>0.0701461774783845</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0428933739812824</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.00348150966699184</v>
+        <v>0.00000570364385065095</v>
       </c>
     </row>
     <row r="12">
@@ -6098,61 +6098,61 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.00282082722521396</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00913991766796016</v>
+        <v>0.0000109040166863764</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.000377714825306893</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.211207728787279</v>
+        <v>0.000810430943903176</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0162101127976053</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.00387122282468237</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.760579534193205</v>
+        <v>0.000386587776779028</v>
       </c>
       <c r="I12" t="n">
-        <v>0.00108286394031163</v>
+        <v>0.00000191829923186251</v>
       </c>
       <c r="J12" t="n">
-        <v>0.450224093549092</v>
+        <v>0.000283403470728319</v>
       </c>
       <c r="K12" t="n">
-        <v>0.24842537660613</v>
+        <v>0.000435352962515322</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.288227770952816</v>
+        <v>0.00375199137128813</v>
       </c>
       <c r="N12" t="n">
-        <v>0.779977036944676</v>
+        <v>0.000521676427949135</v>
       </c>
       <c r="O12" t="n">
-        <v>0.322381254885837</v>
+        <v>0.000140439696395829</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.0049070891735873</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.00245664074577062</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.31445578361848</v>
+        <v>0.0773469356229884</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0192876245419189</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.00604868346184441</v>
+        <v>0.000017365656204229</v>
       </c>
     </row>
     <row r="13">
@@ -6160,61 +6160,61 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.335524175811583</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.749219362170846</v>
+        <v>0.0000686637009914773</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0168271954674221</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2.00988084852935</v>
+        <v>0.000592448375006776</v>
       </c>
       <c r="F13" t="n">
-        <v>0.19844482036304</v>
+        <v>0.0000298139914843826</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.288603611807443</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0576046134541732</v>
+        <v>0.00000224923452925883</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0647438650628426</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.41632560360423</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.58123443560572</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.75199137128813</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.51595926306888</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.934928815391422</v>
+        <v>0.0000312876279001039</v>
       </c>
       <c r="P13" t="n">
-        <v>0.162494752919648</v>
+        <v>0.00000898918213589994</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0291460710701922</v>
+        <v>0.00000745349787109564</v>
       </c>
       <c r="R13" t="n">
-        <v>30.3739470654572</v>
+        <v>0.0779775252297607</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.815837730623854</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.34797935288934</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -6222,61 +6222,61 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.00418716541242698</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00482384543586786</v>
+        <v>0.00000860435283643246</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00160056657223796</v>
+        <v>0.0000511732563429931</v>
       </c>
       <c r="E14" t="n">
-        <v>0.272725564828722</v>
+        <v>0.0015646336342039</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.00671119319646078</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.00922378091391157</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>67.4516255326689</v>
+        <v>0.051259752732033</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0166989018163846</v>
+        <v>0.0000442293926504335</v>
       </c>
       <c r="J14" t="n">
-        <v>0.865963619904364</v>
+        <v>0.000814998262524541</v>
       </c>
       <c r="K14" t="n">
-        <v>0.424489372642386</v>
+        <v>0.0011122258192778</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.521676427949135</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0265099435207127</v>
+        <v>0.00051595926306888</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.49821902318248</v>
+        <v>0.00227849301251073</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.00200170727433162</v>
+        <v>0.00000996293486323759</v>
       </c>
       <c r="R14" t="n">
-        <v>0.759006005664891</v>
+        <v>0.037924515371148</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0109392497401928</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0619638387195922</v>
+        <v>0.000265980170136737</v>
       </c>
     </row>
     <row r="15">
@@ -6284,61 +6284,61 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0639314045339509</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0357133819988814</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.00824362606232295</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0169187205195242</v>
+        <v>0.000149023110633784</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.112438298322243</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.939739340691646</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.87221330233543</v>
+        <v>0.00101766792969354</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.124985295847547</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.59169101571165</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.092410552893375</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.140439696395829</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0312876279001039</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.27849301251073</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.0203293694334331</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.136813659310756</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.250442102954638</v>
+        <v>0.0192123931605113</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.263117743750954</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.17517409306673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -6346,61 +6346,61 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>13.7489102351071</v>
+        <v>0.0874697057344805</v>
       </c>
       <c r="C16" t="n">
-        <v>0.311434231649013</v>
+        <v>0.00051594537596575</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.141902738432483</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.141769931818346</v>
+        <v>0.00075541132763681</v>
       </c>
       <c r="F16" t="n">
-        <v>0.194211606192965</v>
+        <v>0.000527441984886726</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.019665023213666</v>
+        <v>0.0000138800522338612</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01436219541887</v>
+        <v>0.0000353310420498285</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00176432669363734</v>
+        <v>0.00000154222802598458</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00357197897717534</v>
+        <v>0.00000869255796464036</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00353370911132567</v>
+        <v>0.0000049070891735873</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.00898918213589994</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0336055226157056</v>
+        <v>0.0000203293694334331</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0313600806311953</v>
+        <v>0.00014496943444255</v>
       </c>
       <c r="R16" t="n">
-        <v>0.134331250416481</v>
+        <v>0.0062339660861253</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.559341111715649</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.00703335286260978</v>
+        <v>0.000028040509563356</v>
       </c>
     </row>
     <row r="17">
@@ -6408,61 +6408,61 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3.75460918761057</v>
+        <v>0.0051671950264004</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.32021032981647</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0123512747875354</v>
+        <v>0.0000793403974189623</v>
       </c>
       <c r="E17" t="n">
-        <v>0.688747166903678</v>
+        <v>0.000793889236559157</v>
       </c>
       <c r="F17" t="n">
-        <v>11.4946219595197</v>
+        <v>0.00675297179224438</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.167924165589028</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.775080005855807</v>
+        <v>0.000118343360370333</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0875410006483505</v>
+        <v>0.000046585187475354</v>
       </c>
       <c r="J17" t="n">
-        <v>0.00545337341669723</v>
+        <v>0.00000103118253526174</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0105430992390821</v>
+        <v>0.00000555018835155585</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00817801251478226</v>
+        <v>0.00000245664074577062</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.00745349787109564</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.00996293486323759</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.04547939668585</v>
+        <v>0.000136813659310756</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.14496943444255</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.19206296024499</v>
+        <v>0.0119670552951011</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.367904241262274</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-31.5646326444633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -6470,61 +6470,61 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>-4.7218884733066</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>-6.31119777859379</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.33762511803588</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-13.6999799869692</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.75305410915002</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-15.7375873437243</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-16.2274182466387</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-22.6414311494589</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-225.380064038643</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-70.1461774783845</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-77.3469356229884</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-77.9775252297607</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-37.924515371148</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-19.2123931605113</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.2339660861253</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-11.9670552951011</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-14.258736286355</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-17.4092715064105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -6532,61 +6532,61 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2.22627177436203</v>
+        <v>0.0290814196843163</v>
       </c>
       <c r="C19" t="n">
-        <v>0.047815310022199</v>
+        <v>0.000162649371137077</v>
       </c>
       <c r="D19" t="n">
-        <v>0.074480642115203</v>
+        <v>0.00454122801714583</v>
       </c>
       <c r="E19" t="n">
-        <v>0.175344251231896</v>
+        <v>0.00191839895443802</v>
       </c>
       <c r="F19" t="n">
-        <v>0.212486701512558</v>
+        <v>0.00118489347185878</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0130752526017333</v>
+        <v>0.000190573245473885</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0742900876960717</v>
+        <v>0.00010766524744295</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0571068246416974</v>
+        <v>0.000288450743149295</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0121898935196762</v>
+        <v>0.0000218784994803856</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00858427205805042</v>
+        <v>0.0000428933739812824</v>
       </c>
       <c r="L19" t="n">
-        <v>0.006764528870252</v>
+        <v>0.0000192876245419189</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0219804505376535</v>
+        <v>0.000815837730623854</v>
       </c>
       <c r="N19" t="n">
-        <v>0.00573623522428831</v>
+        <v>0.0000109392497401928</v>
       </c>
       <c r="O19" t="n">
-        <v>0.211830673591413</v>
+        <v>0.000263117743750954</v>
       </c>
       <c r="P19" t="n">
-        <v>0.272413550408003</v>
+        <v>0.000559341111715649</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0387603317666031</v>
+        <v>0.000367904241262274</v>
       </c>
       <c r="R19" t="n">
-        <v>0.149639284913159</v>
+        <v>0.014258736286355</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.365347514448265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -6594,58 +6594,58 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3.68018783183286</v>
+        <v>0.0058726738064576</v>
       </c>
       <c r="C20" t="n">
-        <v>0.326159654558504</v>
+        <v>0.000135532709662491</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1445939565628</v>
+        <v>0.00852530283859088</v>
       </c>
       <c r="E20" t="n">
-        <v>0.560580623123581</v>
+        <v>0.000749227913689507</v>
       </c>
       <c r="F20" t="n">
-        <v>26.2853173960736</v>
+        <v>0.0179056152179249</v>
       </c>
       <c r="G20" t="n">
-        <v>17.039957557177</v>
+        <v>0.0303395280760896</v>
       </c>
       <c r="H20" t="n">
-        <v>5.39357954869368</v>
+        <v>0.000954883151392217</v>
       </c>
       <c r="I20" t="n">
-        <v>20.1756359716914</v>
+        <v>0.0124491400671123</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.114039661743286</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.00570364385065095</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.017365656204229</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.517843592465601</v>
+        <v>0.00234797935288934</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.265980170136737</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>27.5159701555148</v>
+        <v>0.00417517409306673</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.028040509563356</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>27.2223090639671</v>
+        <v>0.0315646326444633</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49560433580938</v>
+        <v>0.0174092715064105</v>
       </c>
       <c r="S20" t="n">
-        <v>2.99073330397008</v>
+        <v>0.000365347514448265</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -6738,7 +6738,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000536399745740311</v>
+        <v>0.536399745740311</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -6747,28 +6747,28 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000325168111118902</v>
+        <v>0.325168111118902</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000266840472028371</v>
+        <v>0.266840472028371</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0000230966403530706</v>
+        <v>0.0230966403530706</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0000287486695098467</v>
+        <v>0.0287486695098467</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0000129232790357053</v>
+        <v>0.0129232790357053</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000118084812786089</v>
+        <v>0.118084812786089</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0000286811761214415</v>
+        <v>0.0286811761214415</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000672342214539047</v>
+        <v>0.672342214539047</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.000647318078428321</v>
+        <v>0.64731807842832</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -6791,28 +6791,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00827593243766192</v>
+        <v>8.27593243766192</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0000976251180358829</v>
+        <v>0.0976251180358829</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0000840673593466248</v>
+        <v>0.0840673593466248</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00637635628052044</v>
+        <v>6.37635628052044</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0000556182474729949</v>
+        <v>0.0556182474729949</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0000274705483805371</v>
+        <v>0.0274705483805371</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -6830,16 +6830,16 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0000978036589229499</v>
+        <v>0.09780365892295</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000473130810296564</v>
+        <v>0.473130810296564</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000225300310359146</v>
+        <v>0.225300310359146</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -6853,7 +6853,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.000272320015796632</v>
+        <v>0.272320015796632</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -6862,7 +6862,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000777629651996917</v>
+        <v>0.777629651996917</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -6871,10 +6871,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0000321791288950899</v>
+        <v>0.0321791288950899</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0000329988537600228</v>
+        <v>0.0329988537600228</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -6883,25 +6883,25 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00000807704939731581</v>
+        <v>0.00807704939731582</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0000276423167664775</v>
+        <v>0.0276423167664775</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.000404656844738082</v>
+        <v>0.404656844738082</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00421378757463332</v>
+        <v>4.21378757463332</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00149578560323978</v>
+        <v>1.49578560323978</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -6963,7 +6963,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00157301157083482</v>
+        <v>1.57301157083482</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -6977,16 +6977,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0029959168525915</v>
+        <v>2.9959168525915</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00000292728989612842</v>
+        <v>0.00292728989612842</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000756658858444723</v>
+        <v>0.756658858444723</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -6995,28 +6995,28 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000414355943673812</v>
+        <v>0.414355943673812</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0000372112539021694</v>
+        <v>0.0372112539021694</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0000185512456556526</v>
+        <v>0.0185512456556526</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0000317024188844646</v>
+        <v>0.0317024188844646</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0000196239626094074</v>
+        <v>0.0196239626094074</v>
       </c>
       <c r="O6" t="n">
-        <v>0.000504778125910391</v>
+        <v>0.504778125910391</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -7025,7 +7025,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.000219632682035528</v>
+        <v>0.219632682035528</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -7039,55 +7039,55 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0000662012889417402</v>
+        <v>0.0662012889417402</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000183813899766754</v>
+        <v>0.183813899766754</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0000189565627950897</v>
+        <v>0.0189565627950897</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00193946950154608</v>
+        <v>1.93946950154608</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00871190313745185</v>
+        <v>8.71190313745184</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00470808464858901</v>
+        <v>4.70808464858901</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0105032102926332</v>
+        <v>10.5032102926332</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0000221808371969759</v>
+        <v>0.0221808371969759</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0000197887710234237</v>
+        <v>0.0197887710234237</v>
       </c>
       <c r="M7" t="n">
-        <v>0.000113330396350104</v>
+        <v>0.113330396350104</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0000704953118353326</v>
+        <v>0.0704953118353326</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0110270149002252</v>
+        <v>11.0270149002252</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.000257856291611627</v>
+        <v>0.257856291611627</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00240721334887436</v>
+        <v>2.40721334887436</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -7110,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000674380726151485</v>
+        <v>0.0674380726151485</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.00024680769097526</v>
+        <v>0.246807690975261</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -7172,16 +7172,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000359634637730725</v>
+        <v>0.359634637730725</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00156974808865218</v>
+        <v>1.56974808865218</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0000991196624608015</v>
+        <v>0.0991196624608015</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -7196,13 +7196,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00000881079456978631</v>
+        <v>0.00881079456978631</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00050825455928443</v>
+        <v>0.50825455928443</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -7211,7 +7211,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.00120019582562195</v>
+        <v>1.20019582562195</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -7228,43 +7228,43 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00000736271145474569</v>
+        <v>0.00736271145474569</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000000207743153918791</v>
+        <v>0.000207743153918791</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00135581311186632</v>
+        <v>1.35581311186632</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000003890973961543</v>
+        <v>0.003890973961543</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00313706779407503</v>
+        <v>3.13706779407503</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0000239369923647834</v>
+        <v>0.0239369923647834</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.000671013534631633</v>
+        <v>0.671013534631632</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.000116843855804429</v>
+        <v>0.116843855804429</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.000854970847788536</v>
+        <v>0.854970847788536</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -7273,13 +7273,13 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0042451956072098</v>
+        <v>4.2451956072098</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0000250035694265778</v>
+        <v>0.0250035694265778</v>
       </c>
     </row>
     <row r="11">
@@ -7290,13 +7290,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00000110017527484706</v>
+        <v>0.00110017527484706</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000000528800755429651</v>
+        <v>0.000528800755429651</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000478249866505243</v>
+        <v>0.478249866505243</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -7305,10 +7305,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.000386149546741079</v>
+        <v>0.386149546741079</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0000154450593591816</v>
+        <v>0.0154450593591816</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -7320,13 +7320,13 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.00021287065824151</v>
+        <v>0.21287065824151</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.000371746608797184</v>
+        <v>0.371746608797184</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -7335,13 +7335,13 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.00367836933124744</v>
+        <v>3.67836933124744</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.00000348150966699184</v>
+        <v>0.00348150966699184</v>
       </c>
     </row>
     <row r="12">
@@ -7352,13 +7352,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00000913991766796016</v>
+        <v>0.00913991766796016</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000211207728787279</v>
+        <v>0.211207728787279</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -7367,28 +7367,28 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.000760579534193205</v>
+        <v>0.760579534193205</v>
       </c>
       <c r="I12" t="n">
-        <v>0.00000108286394031163</v>
+        <v>0.00108286394031163</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000450224093549092</v>
+        <v>0.450224093549092</v>
       </c>
       <c r="K12" t="n">
-        <v>0.00024842537660613</v>
+        <v>0.24842537660613</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.000288227770952816</v>
+        <v>0.288227770952816</v>
       </c>
       <c r="N12" t="n">
-        <v>0.000779977036944676</v>
+        <v>0.779977036944676</v>
       </c>
       <c r="O12" t="n">
-        <v>0.000322381254885837</v>
+        <v>0.322381254885837</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -7397,13 +7397,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.00231445578361848</v>
+        <v>2.31445578361848</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.00000604868346184441</v>
+        <v>0.00604868346184441</v>
       </c>
     </row>
     <row r="13">
@@ -7414,22 +7414,22 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.000749219362170846</v>
+        <v>0.749219362170846</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00200988084852935</v>
+        <v>2.00988084852935</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00019844482036304</v>
+        <v>0.19844482036304</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0000576046134541732</v>
+        <v>0.0576046134541732</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7450,16 +7450,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.000934928815391422</v>
+        <v>0.934928815391422</v>
       </c>
       <c r="P13" t="n">
-        <v>0.000162494752919648</v>
+        <v>0.162494752919648</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0000291460710701922</v>
+        <v>0.0291460710701922</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0303739470654572</v>
+        <v>30.3739470654572</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -7476,13 +7476,13 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00000482384543586786</v>
+        <v>0.00482384543586786</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00000160056657223796</v>
+        <v>0.00160056657223796</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000272725564828722</v>
+        <v>0.272725564828722</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7491,43 +7491,43 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0674516255326689</v>
+        <v>67.4516255326689</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0000166989018163846</v>
+        <v>0.0166989018163846</v>
       </c>
       <c r="J14" t="n">
-        <v>0.000865963619904364</v>
+        <v>0.865963619904364</v>
       </c>
       <c r="K14" t="n">
-        <v>0.000424489372642386</v>
+        <v>0.424489372642386</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0000265099435207127</v>
+        <v>0.0265099435207127</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.00349821902318248</v>
+        <v>3.49821902318248</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.00000200170727433162</v>
+        <v>0.00200170727433162</v>
       </c>
       <c r="R14" t="n">
-        <v>0.000759006005664891</v>
+        <v>0.759006005664891</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0000619638387195922</v>
+        <v>0.0619638387195922</v>
       </c>
     </row>
     <row r="15">
@@ -7544,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0000169187205195242</v>
+        <v>0.0169187205195242</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -7553,7 +7553,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00087221330233543</v>
+        <v>0.87221330233543</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.000250442102954638</v>
+        <v>0.250442102954638</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -7597,37 +7597,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0137489102351071</v>
+        <v>13.7489102351071</v>
       </c>
       <c r="C16" t="n">
-        <v>0.000311434231649013</v>
+        <v>0.311434231649013</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000141769931818346</v>
+        <v>0.141769931818346</v>
       </c>
       <c r="F16" t="n">
-        <v>0.000194211606192965</v>
+        <v>0.194211606192965</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.000019665023213666</v>
+        <v>0.019665023213666</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00001436219541887</v>
+        <v>0.01436219541887</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00000176432669363734</v>
+        <v>0.00176432669363734</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00000357197897717534</v>
+        <v>0.00357197897717534</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00000353370911132567</v>
+        <v>0.00353370911132567</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -7636,22 +7636,22 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0000336055226157056</v>
+        <v>0.0336055226157056</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0000313600806311953</v>
+        <v>0.0313600806311953</v>
       </c>
       <c r="R16" t="n">
-        <v>0.000134331250416481</v>
+        <v>0.134331250416481</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.00000703335286260978</v>
+        <v>0.00703335286260978</v>
       </c>
     </row>
     <row r="17">
@@ -7659,37 +7659,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.00375460918761057</v>
+        <v>3.75460918761057</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0000123512747875354</v>
+        <v>0.0123512747875354</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000688747166903678</v>
+        <v>0.688747166903678</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0114946219595197</v>
+        <v>11.4946219595197</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.000775080005855807</v>
+        <v>0.775080005855807</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0000875410006483505</v>
+        <v>0.0875410006483505</v>
       </c>
       <c r="J17" t="n">
-        <v>0.00000545337341669723</v>
+        <v>0.00545337341669723</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0000105430992390821</v>
+        <v>0.0105430992390821</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00000817801251478226</v>
+        <v>0.00817801251478226</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.00104547939668585</v>
+        <v>1.04547939668585</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -7707,7 +7707,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.00119206296024499</v>
+        <v>1.19206296024499</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -7783,55 +7783,55 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.00222627177436203</v>
+        <v>2.22627177436203</v>
       </c>
       <c r="C19" t="n">
-        <v>0.000047815310022199</v>
+        <v>0.047815310022199</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000074480642115203</v>
+        <v>0.074480642115203</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000175344251231896</v>
+        <v>0.175344251231896</v>
       </c>
       <c r="F19" t="n">
-        <v>0.000212486701512558</v>
+        <v>0.212486701512558</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0000130752526017333</v>
+        <v>0.0130752526017333</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0000742900876960717</v>
+        <v>0.0742900876960717</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0000571068246416974</v>
+        <v>0.0571068246416974</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0000121898935196762</v>
+        <v>0.0121898935196762</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00000858427205805042</v>
+        <v>0.00858427205805042</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00000676452887025199</v>
+        <v>0.006764528870252</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0000219804505376535</v>
+        <v>0.0219804505376535</v>
       </c>
       <c r="N19" t="n">
-        <v>0.00000573623522428831</v>
+        <v>0.00573623522428831</v>
       </c>
       <c r="O19" t="n">
-        <v>0.000211830673591413</v>
+        <v>0.211830673591413</v>
       </c>
       <c r="P19" t="n">
-        <v>0.000272413550408003</v>
+        <v>0.272413550408003</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0000387603317666031</v>
+        <v>0.0387603317666031</v>
       </c>
       <c r="R19" t="n">
-        <v>0.000149639284913159</v>
+        <v>0.149639284913159</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -7845,28 +7845,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.00368018783183286</v>
+        <v>3.68018783183286</v>
       </c>
       <c r="C20" t="n">
-        <v>0.000326159654558504</v>
+        <v>0.326159654558504</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0011445939565628</v>
+        <v>1.1445939565628</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000560580623123581</v>
+        <v>0.560580623123581</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0262853173960736</v>
+        <v>26.2853173960736</v>
       </c>
       <c r="G20" t="n">
-        <v>0.017039957557177</v>
+        <v>17.039957557177</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00539357954869368</v>
+        <v>5.39357954869368</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0201756359716914</v>
+        <v>20.1756359716914</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -7878,25 +7878,25 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.000517843592465601</v>
+        <v>0.517843592465601</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0275159701555148</v>
+        <v>27.5159701555148</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0272223090639671</v>
+        <v>27.2223090639671</v>
       </c>
       <c r="R20" t="n">
-        <v>0.00149560433580938</v>
+        <v>1.49560433580938</v>
       </c>
       <c r="S20" t="n">
-        <v>0.00299073330397008</v>
+        <v>2.99073330397008</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -7989,7 +7989,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.536399745740311</v>
+        <v>0.449260811040718</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -7998,28 +7998,28 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.325168111118902</v>
+        <v>0.036075735684963</v>
       </c>
       <c r="I2" t="n">
-        <v>0.266840472028371</v>
+        <v>0.10318057084728</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0230966403530706</v>
+        <v>0.00317343062836571</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0287486695098467</v>
+        <v>0.0109968186357951</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0129232790357053</v>
+        <v>0.00282082722521396</v>
       </c>
       <c r="M2" t="n">
-        <v>0.118084812786089</v>
+        <v>0.335524175811583</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0286811761214415</v>
+        <v>0.00418716541242698</v>
       </c>
       <c r="O2" t="n">
-        <v>0.672342214539047</v>
+        <v>0.0639314045339509</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.64731807842832</v>
+        <v>4.7218884733066</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -8042,28 +8042,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>8.27593243766192</v>
+        <v>31.7811016799761</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0976251180358829</v>
+        <v>1.74987108907789</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0840673593466248</v>
+        <v>0.270389231010488</v>
       </c>
       <c r="F3" t="n">
-        <v>6.37635628052044</v>
+        <v>10.4528499151892</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0556182474729949</v>
+        <v>0.0236960828428597</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0274705483805371</v>
+        <v>0.040791114036637</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -8081,16 +8081,16 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.09780365892295</v>
+        <v>0.0357133819988814</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.473130810296564</v>
+        <v>1.32021032981647</v>
       </c>
       <c r="R3" t="n">
-        <v>0.225300310359146</v>
+        <v>6.31119777859379</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -8104,7 +8104,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.272320015796632</v>
+        <v>0.058342776203966</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -8113,7 +8113,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.777629651996917</v>
+        <v>0.139537299338999</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -8122,10 +8122,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0321791288950899</v>
+        <v>0.000764872521246459</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0329988537600228</v>
+        <v>0.00273371104815864</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -8134,25 +8134,25 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00807704939731582</v>
+        <v>0.000377714825306893</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0276423167664775</v>
+        <v>0.0168271954674221</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.404656844738082</v>
+        <v>0.00824362606232295</v>
       </c>
       <c r="P4" t="n">
-        <v>4.21378757463332</v>
+        <v>0.141902738432483</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49578560323978</v>
+        <v>2.33762511803588</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.57301157083482</v>
+        <v>13.6999799869692</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -8228,16 +8228,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2.9959168525915</v>
+        <v>7.01810122379124</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00292728989612842</v>
+        <v>0.032007229090813</v>
       </c>
       <c r="E6" t="n">
-        <v>0.756658858444723</v>
+        <v>1.48456755962018</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -8246,28 +8246,28 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.414355943673812</v>
+        <v>0.107688838521671</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0372112539021694</v>
+        <v>0.01197689862753</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0185512456556526</v>
+        <v>0.0166231093020029</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0317024188844646</v>
+        <v>0.0162101127976053</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0196239626094074</v>
+        <v>0.00671119319646078</v>
       </c>
       <c r="O6" t="n">
-        <v>0.504778125910391</v>
+        <v>0.112438298322243</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -8276,7 +8276,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.219632682035528</v>
+        <v>3.75305410915002</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -8290,55 +8290,55 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0662012889417402</v>
+        <v>0.0593324151293155</v>
       </c>
       <c r="C7" t="n">
-        <v>0.183813899766754</v>
+        <v>0.0428994692612761</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0189565627950897</v>
+        <v>0.0793008144954068</v>
       </c>
       <c r="E7" t="n">
-        <v>1.93946950154608</v>
+        <v>1.45585629799662</v>
       </c>
       <c r="F7" t="n">
-        <v>8.71190313745184</v>
+        <v>3.33310310091466</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.70808464858901</v>
+        <v>0.468141445870518</v>
       </c>
       <c r="I7" t="n">
-        <v>10.5032102926332</v>
+        <v>3.63993701204446</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0221808371969759</v>
+        <v>0.00760418769134037</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0197887710234237</v>
+        <v>0.00387122282468237</v>
       </c>
       <c r="M7" t="n">
-        <v>0.113330396350104</v>
+        <v>0.288603611807443</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0704953118353326</v>
+        <v>0.00922378091391157</v>
       </c>
       <c r="O7" t="n">
-        <v>11.0270149002252</v>
+        <v>0.939739340691646</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.257856291611627</v>
+        <v>0.167924165589028</v>
       </c>
       <c r="R7" t="n">
-        <v>2.40721334887436</v>
+        <v>15.7375873437243</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -8361,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0674380726151485</v>
+        <v>0.509105600976021</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -8400,7 +8400,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.246807690975261</v>
+        <v>16.2274182466387</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -8423,16 +8423,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.359634637730725</v>
+        <v>0.778978122956807</v>
       </c>
       <c r="F9" t="n">
-        <v>1.56974808865218</v>
+        <v>1.73298125437135</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0991196624608015</v>
+        <v>0.0284394266429212</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -8447,13 +8447,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00881079456978631</v>
+        <v>0.0647438650628426</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.50825455928443</v>
+        <v>0.124985295847547</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -8462,7 +8462,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.20019582562195</v>
+        <v>22.6414311494589</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -8479,43 +8479,43 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00736271145474569</v>
+        <v>0.0139542202133135</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000207743153918791</v>
+        <v>0.00705730677454936</v>
       </c>
       <c r="E10" t="n">
-        <v>1.35581311186632</v>
+        <v>8.26474780634044</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003890973961543</v>
+        <v>0.0315974871496869</v>
       </c>
       <c r="H10" t="n">
-        <v>3.13706779407503</v>
+        <v>2.53309195205587</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0239369923647834</v>
+        <v>0.0673652010297894</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.671013534631632</v>
+        <v>1.86810118189037</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.116843855804429</v>
+        <v>2.41632560360423</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.854970847788536</v>
+        <v>0.59169101571165</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -8524,13 +8524,13 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>4.2451956072098</v>
+        <v>225.380064038643</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0250035694265778</v>
+        <v>0.114039661743286</v>
       </c>
     </row>
     <row r="11">
@@ -8541,13 +8541,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00110017527484706</v>
+        <v>0.000748963333923862</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000528800755429651</v>
+        <v>0.00645260718457481</v>
       </c>
       <c r="E11" t="n">
-        <v>0.478249866505243</v>
+        <v>1.04716596595386</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -8556,10 +8556,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.386149546741079</v>
+        <v>0.111998824703691</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0154450593591816</v>
+        <v>0.0156130048841051</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -8571,13 +8571,13 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.21287065824151</v>
+        <v>1.58123443560572</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.371746608797184</v>
+        <v>0.092410552893375</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -8586,13 +8586,13 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.67836933124744</v>
+        <v>70.1461774783845</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.00348150966699184</v>
+        <v>0.00570364385065095</v>
       </c>
     </row>
     <row r="12">
@@ -8603,13 +8603,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00913991766796016</v>
+        <v>0.0109040166863764</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.211207728787279</v>
+        <v>0.810430943903176</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -8618,28 +8618,28 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.760579534193205</v>
+        <v>0.386587776779028</v>
       </c>
       <c r="I12" t="n">
-        <v>0.00108286394031163</v>
+        <v>0.00191829923186251</v>
       </c>
       <c r="J12" t="n">
-        <v>0.450224093549092</v>
+        <v>0.283403470728319</v>
       </c>
       <c r="K12" t="n">
-        <v>0.24842537660613</v>
+        <v>0.435352962515322</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.288227770952816</v>
+        <v>3.75199137128813</v>
       </c>
       <c r="N12" t="n">
-        <v>0.779977036944676</v>
+        <v>0.521676427949135</v>
       </c>
       <c r="O12" t="n">
-        <v>0.322381254885837</v>
+        <v>0.140439696395829</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -8648,13 +8648,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.31445578361848</v>
+        <v>77.3469356229884</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.00604868346184441</v>
+        <v>0.017365656204229</v>
       </c>
     </row>
     <row r="13">
@@ -8665,22 +8665,22 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.749219362170846</v>
+        <v>0.0686637009914773</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2.00988084852935</v>
+        <v>0.592448375006776</v>
       </c>
       <c r="F13" t="n">
-        <v>0.19844482036304</v>
+        <v>0.0298139914843826</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0576046134541732</v>
+        <v>0.00224923452925883</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -8701,16 +8701,16 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.934928815391422</v>
+        <v>0.0312876279001039</v>
       </c>
       <c r="P13" t="n">
-        <v>0.162494752919648</v>
+        <v>0.00898918213589994</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0291460710701922</v>
+        <v>0.00745349787109564</v>
       </c>
       <c r="R13" t="n">
-        <v>30.3739470654572</v>
+        <v>77.9775252297607</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -8727,13 +8727,13 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00482384543586786</v>
+        <v>0.00860435283643246</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00160056657223796</v>
+        <v>0.0511732563429931</v>
       </c>
       <c r="E14" t="n">
-        <v>0.272725564828722</v>
+        <v>1.5646336342039</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -8742,43 +8742,43 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>67.4516255326689</v>
+        <v>51.259752732033</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0166989018163846</v>
+        <v>0.0442293926504335</v>
       </c>
       <c r="J14" t="n">
-        <v>0.865963619904364</v>
+        <v>0.814998262524541</v>
       </c>
       <c r="K14" t="n">
-        <v>0.424489372642386</v>
+        <v>1.1122258192778</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0265099435207127</v>
+        <v>0.51595926306888</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.49821902318248</v>
+        <v>2.27849301251073</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.00200170727433162</v>
+        <v>0.00996293486323759</v>
       </c>
       <c r="R14" t="n">
-        <v>0.759006005664891</v>
+        <v>37.924515371148</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0619638387195922</v>
+        <v>0.265980170136737</v>
       </c>
     </row>
     <row r="15">
@@ -8795,7 +8795,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0169187205195242</v>
+        <v>0.149023110633784</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -8804,7 +8804,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.87221330233543</v>
+        <v>1.01766792969354</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.250442102954638</v>
+        <v>19.2123931605113</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -8848,37 +8848,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>13.7489102351071</v>
+        <v>87.4697057344805</v>
       </c>
       <c r="C16" t="n">
-        <v>0.311434231649013</v>
+        <v>0.51594537596575</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.141769931818346</v>
+        <v>0.75541132763681</v>
       </c>
       <c r="F16" t="n">
-        <v>0.194211606192965</v>
+        <v>0.527441984886726</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.019665023213666</v>
+        <v>0.0138800522338612</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01436219541887</v>
+        <v>0.0353310420498286</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00176432669363734</v>
+        <v>0.00154222802598458</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00357197897717534</v>
+        <v>0.00869255796464036</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00353370911132567</v>
+        <v>0.0049070891735873</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -8887,22 +8887,22 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0336055226157056</v>
+        <v>0.0203293694334331</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0313600806311953</v>
+        <v>0.14496943444255</v>
       </c>
       <c r="R16" t="n">
-        <v>0.134331250416481</v>
+        <v>6.2339660861253</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.00703335286260978</v>
+        <v>0.028040509563356</v>
       </c>
     </row>
     <row r="17">
@@ -8910,37 +8910,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3.75460918761057</v>
+        <v>5.1671950264004</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0123512747875354</v>
+        <v>0.0793403974189622</v>
       </c>
       <c r="E17" t="n">
-        <v>0.688747166903678</v>
+        <v>0.793889236559157</v>
       </c>
       <c r="F17" t="n">
-        <v>11.4946219595197</v>
+        <v>6.75297179224438</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.775080005855807</v>
+        <v>0.118343360370333</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0875410006483505</v>
+        <v>0.046585187475354</v>
       </c>
       <c r="J17" t="n">
-        <v>0.00545337341669723</v>
+        <v>0.00103118253526174</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0105430992390821</v>
+        <v>0.00555018835155585</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00817801251478226</v>
+        <v>0.00245664074577062</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -8949,7 +8949,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.04547939668585</v>
+        <v>0.136813659310756</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -8958,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.19206296024499</v>
+        <v>11.9670552951011</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -9034,55 +9034,55 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2.22627177436203</v>
+        <v>29.0814196843163</v>
       </c>
       <c r="C19" t="n">
-        <v>0.047815310022199</v>
+        <v>0.162649371137077</v>
       </c>
       <c r="D19" t="n">
-        <v>0.074480642115203</v>
+        <v>4.54122801714583</v>
       </c>
       <c r="E19" t="n">
-        <v>0.175344251231896</v>
+        <v>1.91839895443802</v>
       </c>
       <c r="F19" t="n">
-        <v>0.212486701512558</v>
+        <v>1.18489347185878</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0130752526017333</v>
+        <v>0.190573245473885</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0742900876960717</v>
+        <v>0.10766524744295</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0571068246416974</v>
+        <v>0.288450743149295</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0121898935196762</v>
+        <v>0.0218784994803856</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00858427205805042</v>
+        <v>0.0428933739812824</v>
       </c>
       <c r="L19" t="n">
-        <v>0.006764528870252</v>
+        <v>0.0192876245419189</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0219804505376535</v>
+        <v>0.815837730623854</v>
       </c>
       <c r="N19" t="n">
-        <v>0.00573623522428831</v>
+        <v>0.0109392497401928</v>
       </c>
       <c r="O19" t="n">
-        <v>0.211830673591413</v>
+        <v>0.263117743750954</v>
       </c>
       <c r="P19" t="n">
-        <v>0.272413550408003</v>
+        <v>0.559341111715649</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0387603317666031</v>
+        <v>0.367904241262274</v>
       </c>
       <c r="R19" t="n">
-        <v>0.149639284913159</v>
+        <v>14.258736286355</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -9096,28 +9096,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3.68018783183286</v>
+        <v>5.8726738064576</v>
       </c>
       <c r="C20" t="n">
-        <v>0.326159654558504</v>
+        <v>0.135532709662491</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1445939565628</v>
+        <v>8.52530283859088</v>
       </c>
       <c r="E20" t="n">
-        <v>0.560580623123581</v>
+        <v>0.749227913689507</v>
       </c>
       <c r="F20" t="n">
-        <v>26.2853173960736</v>
+        <v>17.9056152179249</v>
       </c>
       <c r="G20" t="n">
-        <v>17.039957557177</v>
+        <v>30.3395280760896</v>
       </c>
       <c r="H20" t="n">
-        <v>5.39357954869368</v>
+        <v>0.954883151392217</v>
       </c>
       <c r="I20" t="n">
-        <v>20.1756359716914</v>
+        <v>12.4491400671123</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -9129,25 +9129,25 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.517843592465601</v>
+        <v>2.34797935288934</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>27.5159701555148</v>
+        <v>4.17517409306673</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>27.2223090639671</v>
+        <v>31.5646326444633</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49560433580938</v>
+        <v>17.4092715064105</v>
       </c>
       <c r="S20" t="n">
-        <v>2.99073330397008</v>
+        <v>0.365347514448265</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
